--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/causalidade_granger.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/causalidade_granger.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.893055266886101</v>
+        <v>4.893055266886677</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02722677540617342</v>
+        <v>0.0272267754061644</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.038600146099988</v>
+        <v>2.038600146099545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1537133089935869</v>
+        <v>0.1537133089936316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.835545351987975</v>
+        <v>3.835545351987701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0504991795368231</v>
+        <v>0.05049917953683125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02464825733998097</v>
+        <v>0.02464825733998416</v>
       </c>
       <c r="E5" t="n">
-        <v>0.875283518944416</v>
+        <v>0.8752835189444079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -573,14 +573,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3532338887155382</v>
+        <v>0.5909592002588592</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5524443200016023</v>
+        <v>0.4422592492753611</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -601,14 +601,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5909592002586973</v>
+        <v>0.3532338887154503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4422592492754235</v>
+        <v>0.5524443200016517</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.979914665654492</v>
+        <v>7.979914665654343</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004839248833168957</v>
+        <v>0.004839248833169355</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1442329316474198</v>
+        <v>0.1442329316474225</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7042023037257171</v>
+        <v>0.7042023037257145</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>22.78405011468161</v>
       </c>
       <c r="E10" t="n">
-        <v>2.129209794290445e-06</v>
+        <v>2.12920979429045e-06</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05778181516146766</v>
+        <v>0.05778181516146565</v>
       </c>
       <c r="E11" t="n">
-        <v>0.810094078236569</v>
+        <v>0.8100940782365722</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -741,14 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.07036649734775299</v>
+        <v>1.044205516382787</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7908674021272942</v>
+        <v>0.3071324185177385</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -769,14 +769,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.044205516382798</v>
+        <v>0.07036649734774612</v>
       </c>
       <c r="E13" t="n">
-        <v>0.307132418517736</v>
+        <v>0.7908674021273042</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.890296515384496</v>
+        <v>4.89029651538468</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02727005963427396</v>
+        <v>0.02727005963427107</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.384990038996632</v>
+        <v>2.384990038996912</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1228731215954766</v>
+        <v>0.1228731215954547</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.03533412039150444</v>
+        <v>0.03533412039152043</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8509415414608732</v>
+        <v>0.8509415414608398</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.009378131950339111</v>
+        <v>0.009378131950341232</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9228753943411087</v>
+        <v>0.9228753943410999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -909,14 +909,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2581942651916294</v>
+        <v>0.7557424939264854</v>
       </c>
       <c r="E18" t="n">
-        <v>0.611493594172876</v>
+        <v>0.3849064634773333</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -937,14 +937,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.7557424939267343</v>
+        <v>0.2581942651916005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.384906463477255</v>
+        <v>0.6114935941728959</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3.482439795439833</v>
+        <v>3.48243979543985</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01558279559988806</v>
+        <v>0.01558279559988769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.7194046709746004</v>
+        <v>0.7194046709745979</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5405576737476081</v>
+        <v>0.5405576737476097</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9470781894589665</v>
+        <v>0.9470781894589582</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4173231274668414</v>
+        <v>0.417323127466846</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3060428336509831</v>
+        <v>0.3060428336509923</v>
       </c>
       <c r="E23" t="n">
-        <v>0.821038883325318</v>
+        <v>0.8210388833253113</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1077,14 +1077,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.828451741033782</v>
+        <v>1.385992581641818</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03768610987299542</v>
+        <v>0.2457928822193087</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1105,14 +1105,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.385992581641827</v>
+        <v>2.828451741033805</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2457928822193062</v>
+        <v>0.03768610987299432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4.912132244285448</v>
+        <v>4.912132244285932</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0269294138055102</v>
+        <v>0.0269294138055027</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.377773622969295</v>
+        <v>2.3777736229694</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1234402679079028</v>
+        <v>0.1234402679078945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.258762242556681</v>
+        <v>1.258762242556603</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2621982981297839</v>
+        <v>0.2621982981297987</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.002301988421499822</v>
+        <v>0.002301988421495759</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9617440724799904</v>
+        <v>0.9617440724800241</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1524223649616752</v>
+        <v>0.5188237216693028</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6963276952160896</v>
+        <v>0.4715393754140494</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5188237216693316</v>
+        <v>0.1524223649616141</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4715393754140371</v>
+        <v>0.6963276952161475</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.024971657406305</v>
+        <v>7.024971657406268</v>
       </c>
       <c r="E32" t="n">
-        <v>0.008185611694665697</v>
+        <v>0.008185611694665865</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0004277369686769625</v>
+        <v>0.0004277369686772457</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9835042769060823</v>
+        <v>0.9835042769060769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.314911826639659</v>
+        <v>1.314911826639676</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2518258273299123</v>
+        <v>0.2518258273299091</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.2071574674644359</v>
+        <v>0.2071574674644373</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6491192780454657</v>
+        <v>0.6491192780454644</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.3591132820305983</v>
+        <v>0.8019259428801124</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5491567543824862</v>
+        <v>0.3707684488708616</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1441,14 +1441,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.8019259428801064</v>
+        <v>0.3591132820305764</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3707684488708634</v>
+        <v>0.5491567543824983</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.470047887911877</v>
+        <v>5.470047887912226</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01957301791687723</v>
+        <v>0.01957301791687335</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.780209257912758</v>
+        <v>2.780209257912533</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0957993455182624</v>
+        <v>0.09579934551827589</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7.620336571145278</v>
+        <v>7.620336571144631</v>
       </c>
       <c r="E40" t="n">
-        <v>0.005894056100623227</v>
+        <v>0.005894056100625331</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.04609225504272257</v>
+        <v>0.04609225504273267</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8300590240564975</v>
+        <v>0.830059024056479</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.3239528005394721</v>
+        <v>0.1571698492313364</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5693902275803915</v>
+        <v>0.6918738809076167</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1609,14 +1609,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.1571698492313552</v>
+        <v>0.3239528005394757</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6918738809075993</v>
+        <v>0.5693902275803893</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7.539650548885581</v>
+        <v>7.539650548885707</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006161425221515054</v>
+        <v>0.006161425221514623</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.01429874465185075</v>
+        <v>0.01429874465185212</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9048458511427558</v>
+        <v>0.9048458511427513</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.390378251846203</v>
+        <v>4.390378251846198</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03643387119000646</v>
+        <v>0.03643387119000653</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.09490276669144788</v>
+        <v>0.09490276669144763</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7581089608455397</v>
+        <v>0.75810896084554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1747934472968635</v>
+        <v>0.4361201295837315</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6759906370825902</v>
+        <v>0.5091777078547454</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1777,14 +1777,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.4361201295837331</v>
+        <v>0.1747934472968524</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5091777078547447</v>
+        <v>0.6759906370825998</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
